--- a/data/trans_orig/P64B-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P64B-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32163</t>
+          <t>31192</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58225</t>
+          <t>57295</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16411</t>
+          <t>16840</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38544</t>
+          <t>40001</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68295</t>
+          <t>69386</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21352</t>
+          <t>22804</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43089</t>
+          <t>43788</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31402</t>
+          <t>32614</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55798</t>
+          <t>56362</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>59359</t>
+          <t>57140</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90266</t>
+          <t>89627</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>876</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>7738</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9216</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13545</t>
+          <t>12230</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>991</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9286</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>7224</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21130</t>
+          <t>23230</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10064</t>
+          <t>9982</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27069</t>
+          <t>25527</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>102183</t>
+          <t>101568</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>136458</t>
+          <t>138492</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>79158</t>
+          <t>79436</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107726</t>
+          <t>109106</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>188501</t>
+          <t>189257</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>234528</t>
+          <t>235812</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,68%</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>133480</t>
+          <t>131587</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>169363</t>
+          <t>170149</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41846</t>
+          <t>42572</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68009</t>
+          <t>67466</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>183111</t>
+          <t>179767</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>229396</t>
+          <t>228204</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,33%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19415</t>
+          <t>18843</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13137</t>
+          <t>12719</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9636</t>
+          <t>9844</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26439</t>
+          <t>27085</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55874</t>
+          <t>54224</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84398</t>
+          <t>85968</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20888</t>
+          <t>21138</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41236</t>
+          <t>41630</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>81633</t>
+          <t>81267</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>119593</t>
+          <t>117326</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,58%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7869</t>
+          <t>8989</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6585</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>980</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10385</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13477</t>
+          <t>13693</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>6951</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21893</t>
+          <t>21711</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11991</t>
+          <t>12891</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30712</t>
+          <t>30698</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86106</t>
+          <t>86172</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>118610</t>
+          <t>118750</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>78555</t>
+          <t>77960</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>109355</t>
+          <t>108953</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>173622</t>
+          <t>172946</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>218790</t>
+          <t>216908</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,6%</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>63827</t>
+          <t>65339</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97264</t>
+          <t>96086</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70270</t>
+          <t>70729</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>100478</t>
+          <t>99413</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>142510</t>
+          <t>143723</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>186311</t>
+          <t>185822</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,35%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8158</t>
+          <t>7710</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24695</t>
+          <t>24668</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12337</t>
+          <t>12608</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,47 +2372,47 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
+          <t>4,84%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>22,17%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>21770</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>14206</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>33075</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
           <t>5,07%</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>21,69%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>21770</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>13038</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>32218</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44737</t>
+          <t>45887</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>75052</t>
+          <t>73506</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4735</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15738</t>
+          <t>17082</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>52876</t>
+          <t>53673</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>85118</t>
+          <t>85722</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>874</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>8262</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>883</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12843</t>
+          <t>13991</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9709</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17827</t>
+          <t>18484</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47663</t>
+          <t>47533</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>74972</t>
+          <t>74472</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12270</t>
+          <t>10431</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52460</t>
+          <t>51064</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>82392</t>
+          <t>80681</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -2887,12 +2887,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>209535</t>
+          <t>210188</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>247202</t>
+          <t>246768</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24337</t>
+          <t>23675</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>38826</t>
+          <t>38865</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>239220</t>
+          <t>239583</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>279489</t>
+          <t>280163</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>65,25%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32901</t>
+          <t>32470</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>59815</t>
+          <t>58542</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13375</t>
+          <t>14987</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35245</t>
+          <t>37308</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>53234</t>
+          <t>52348</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>86412</t>
+          <t>89223</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>115385</t>
+          <t>115606</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>159059</t>
+          <t>157921</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>58158</t>
+          <t>58514</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>90505</t>
+          <t>87980</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>183016</t>
+          <t>185489</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>235358</t>
+          <t>238447</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,94%</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14843</t>
+          <t>14729</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>36753</t>
+          <t>35436</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>12790</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>19981</t>
+          <t>19702</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>42541</t>
+          <t>42370</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -3456,12 +3456,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6759</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21928</t>
+          <t>21519</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8726</t>
+          <t>7923</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>24387</t>
+          <t>23995</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>18326</t>
+          <t>18183</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>39429</t>
+          <t>40137</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>145964</t>
+          <t>146551</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>193531</t>
+          <t>192425</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>43188</t>
+          <t>42984</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>71758</t>
+          <t>70252</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>199230</t>
+          <t>199502</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>253642</t>
+          <t>253113</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -3682,12 +3682,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>279487</t>
+          <t>280367</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>334097</t>
+          <t>334323</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3697,12 +3697,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3717,12 +3717,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>111833</t>
+          <t>111320</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>147030</t>
+          <t>145995</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3732,12 +3732,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>404362</t>
+          <t>401860</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>466745</t>
+          <t>470541</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3767,12 +3767,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>47,24%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6523</t>
+          <t>6630</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1610</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>14129</t>
+          <t>13656</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>15723</t>
+          <t>16940</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -4025,12 +4025,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>31638</t>
+          <t>32315</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>56662</t>
+          <t>56359</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4040,12 +4040,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4060,12 +4060,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>29393</t>
+          <t>29893</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>52768</t>
+          <t>53832</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>66489</t>
+          <t>68114</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>101525</t>
+          <t>100631</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4110,12 +4110,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,81%</t>
         </is>
       </c>
     </row>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13407</t>
+          <t>15097</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>8690</t>
+          <t>7565</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>17134</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4223,12 +4223,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -4251,12 +4251,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2477</t>
+          <t>2678</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13730</t>
+          <t>14216</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4266,12 +4266,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7540</t>
+          <t>7019</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>23713</t>
+          <t>22686</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>13420</t>
+          <t>12510</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>32231</t>
+          <t>32102</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -4364,12 +4364,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>47403</t>
+          <t>45260</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>72590</t>
+          <t>71377</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>94517</t>
+          <t>94450</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>124247</t>
+          <t>124344</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>148931</t>
+          <t>146791</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>188223</t>
+          <t>187912</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,19%</t>
         </is>
       </c>
     </row>
@@ -4477,12 +4477,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>53458</t>
+          <t>53871</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>80270</t>
+          <t>80250</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4492,12 +4492,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>25052</t>
+          <t>25807</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>47617</t>
+          <t>48157</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>84701</t>
+          <t>85672</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>121511</t>
+          <t>122630</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,45%</t>
         </is>
       </c>
     </row>
@@ -4707,12 +4707,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>96400</t>
+          <t>96551</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>137699</t>
+          <t>138651</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4722,12 +4722,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>36087</t>
+          <t>36961</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>66480</t>
+          <t>69322</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>140124</t>
+          <t>141147</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>193215</t>
+          <t>194434</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -4820,12 +4820,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>304291</t>
+          <t>305539</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>369430</t>
+          <t>371867</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4835,12 +4835,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>172749</t>
+          <t>172207</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>220258</t>
+          <t>224034</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>492246</t>
+          <t>491052</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>580308</t>
+          <t>574535</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -4933,12 +4933,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>26397</t>
+          <t>25209</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>52465</t>
+          <t>50374</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4948,12 +4948,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>6458</t>
+          <t>6718</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>21824</t>
+          <t>21241</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>37533</t>
+          <t>34962</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>69511</t>
+          <t>64702</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -5046,12 +5046,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>26502</t>
+          <t>25803</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>50739</t>
+          <t>49959</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5061,12 +5061,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>45014</t>
+          <t>45585</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>74544</t>
+          <t>75047</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>76819</t>
+          <t>76593</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>116185</t>
+          <t>116871</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -5159,12 +5159,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>472552</t>
+          <t>469563</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>547540</t>
+          <t>545127</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5174,12 +5174,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5194,12 +5194,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>327297</t>
+          <t>325894</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>392476</t>
+          <t>386996</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>816682</t>
+          <t>812345</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>910113</t>
+          <t>906248</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -5272,12 +5272,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>797777</t>
+          <t>793426</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>884287</t>
+          <t>880888</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5307,12 +5307,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>302321</t>
+          <t>303123</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>364824</t>
+          <t>363157</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5342,12 +5342,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1116869</t>
+          <t>1120141</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1224480</t>
+          <t>1226800</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,62%</t>
         </is>
       </c>
     </row>
@@ -5735,12 +5735,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17097</t>
+          <t>16256</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39356</t>
+          <t>38004</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15666</t>
+          <t>18283</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23450</t>
+          <t>23372</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49183</t>
+          <t>48239</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -5848,12 +5848,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34283</t>
+          <t>34805</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61302</t>
+          <t>61899</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5863,12 +5863,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24242</t>
+          <t>23082</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46157</t>
+          <t>46257</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62795</t>
+          <t>61415</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98800</t>
+          <t>97527</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -5961,12 +5961,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9269</t>
+          <t>10142</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5976,12 +5976,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11031</t>
+          <t>11195</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -6074,12 +6074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4209</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16590</t>
+          <t>16198</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6109,12 +6109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17652</t>
+          <t>17522</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6124,12 +6124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6144,12 +6144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11300</t>
+          <t>11856</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28246</t>
+          <t>29444</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6159,12 +6159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>84883</t>
+          <t>84148</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>117078</t>
+          <t>119265</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>75283</t>
+          <t>74442</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>103662</t>
+          <t>102432</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>168461</t>
+          <t>167746</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>214545</t>
+          <t>210866</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,37%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92916</t>
+          <t>91867</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>128362</t>
+          <t>126280</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37808</t>
+          <t>38037</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>64146</t>
+          <t>63744</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>138073</t>
+          <t>139669</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>180884</t>
+          <t>182365</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,51%</t>
         </is>
       </c>
     </row>
@@ -6530,12 +6530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18412</t>
+          <t>17383</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6545,12 +6545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6565,12 +6565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11436</t>
+          <t>12343</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6580,12 +6580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6600,12 +6600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7172</t>
+          <t>7485</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23928</t>
+          <t>24939</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6615,12 +6615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -6643,12 +6643,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>71599</t>
+          <t>69862</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>105268</t>
+          <t>104235</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6678,12 +6678,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>12170</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30830</t>
+          <t>31374</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6693,12 +6693,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6713,12 +6713,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>87691</t>
+          <t>89588</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>125880</t>
+          <t>127749</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6728,12 +6728,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,53%</t>
         </is>
       </c>
     </row>
@@ -6796,7 +6796,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10387</t>
+          <t>10682</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>10439</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -6869,12 +6869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2087</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16158</t>
+          <t>16353</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6904,12 +6904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>4042</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19062</t>
+          <t>19705</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6939,12 +6939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8860</t>
+          <t>8740</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29417</t>
+          <t>29158</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -6982,12 +6982,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>64163</t>
+          <t>65747</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>96008</t>
+          <t>97369</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7017,12 +7017,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>65304</t>
+          <t>63551</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>93128</t>
+          <t>90915</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7052,12 +7052,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>137757</t>
+          <t>136044</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>179660</t>
+          <t>177215</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,35%</t>
         </is>
       </c>
     </row>
@@ -7095,12 +7095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53506</t>
+          <t>54269</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85091</t>
+          <t>85780</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7110,12 +7110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7130,12 +7130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39944</t>
+          <t>41106</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63556</t>
+          <t>67283</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7145,12 +7145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7165,12 +7165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>101676</t>
+          <t>102323</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>139839</t>
+          <t>141100</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,72%</t>
         </is>
       </c>
     </row>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5534</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19209</t>
+          <t>18770</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7340,12 +7340,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7360,12 +7360,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17425</t>
+          <t>16115</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7395,12 +7395,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12651</t>
+          <t>12339</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>31114</t>
+          <t>30015</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -7438,12 +7438,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34626</t>
+          <t>34665</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58704</t>
+          <t>59218</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7453,12 +7453,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7473,12 +7473,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4192</t>
+          <t>4284</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15660</t>
+          <t>16275</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42431</t>
+          <t>43074</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>69647</t>
+          <t>68973</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -7551,12 +7551,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>904</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10354</t>
+          <t>9590</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7566,12 +7566,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7621,12 +7621,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>947</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9763</t>
+          <t>8895</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -7664,12 +7664,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>950</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>8447</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>949</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>9070</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7749,12 +7749,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -7777,12 +7777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38383</t>
+          <t>38215</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63700</t>
+          <t>64340</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7812,12 +7812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9124</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23594</t>
+          <t>24247</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7827,12 +7827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51925</t>
+          <t>52488</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>83338</t>
+          <t>80953</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7862,12 +7862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,22%</t>
         </is>
       </c>
     </row>
@@ -7890,12 +7890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>142387</t>
+          <t>141375</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>174409</t>
+          <t>172758</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7925,12 +7925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>66754</t>
+          <t>66840</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>84955</t>
+          <t>85570</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7940,12 +7940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7960,12 +7960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>216081</t>
+          <t>214595</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>252809</t>
+          <t>252348</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7975,12 +7975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,13%</t>
         </is>
       </c>
     </row>
@@ -8120,12 +8120,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18881</t>
+          <t>18448</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40601</t>
+          <t>40010</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16664</t>
+          <t>16300</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36225</t>
+          <t>36884</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40611</t>
+          <t>39148</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>70034</t>
+          <t>67993</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -8233,12 +8233,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>114164</t>
+          <t>113838</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>155115</t>
+          <t>155207</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8268,12 +8268,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>49001</t>
+          <t>48944</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>77128</t>
+          <t>75971</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8283,12 +8283,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8303,12 +8303,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>173126</t>
+          <t>173725</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>222770</t>
+          <t>219863</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8318,12 +8318,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -8346,12 +8346,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>18799</t>
+          <t>18345</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>43512</t>
+          <t>42201</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8361,12 +8361,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8381,12 +8381,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>12077</t>
+          <t>11496</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8416,12 +8416,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>23530</t>
+          <t>22556</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>47950</t>
+          <t>47961</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -8459,12 +8459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11632</t>
+          <t>11577</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8494,12 +8494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>22985</t>
+          <t>23244</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>44912</t>
+          <t>44363</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8509,12 +8509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8529,12 +8529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>26860</t>
+          <t>26149</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>50535</t>
+          <t>49814</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8544,12 +8544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -8572,12 +8572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>57848</t>
+          <t>56733</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>88732</t>
+          <t>88211</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8587,12 +8587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8607,12 +8607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>65209</t>
+          <t>63897</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>96208</t>
+          <t>94501</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8622,12 +8622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8642,12 +8642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>126044</t>
+          <t>130822</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>173482</t>
+          <t>176849</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8657,12 +8657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,44%</t>
         </is>
       </c>
     </row>
@@ -8685,12 +8685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>138846</t>
+          <t>137587</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>178569</t>
+          <t>179118</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8720,12 +8720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>79122</t>
+          <t>78522</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>111605</t>
+          <t>111650</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>225551</t>
+          <t>230008</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>279045</t>
+          <t>279504</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,62%</t>
         </is>
       </c>
     </row>
@@ -8915,12 +8915,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>12374</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8930,12 +8930,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8950,12 +8950,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11933</t>
+          <t>11173</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>29071</t>
+          <t>28670</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8985,12 +8985,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>14946</t>
+          <t>15563</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>34638</t>
+          <t>34513</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9000,12 +9000,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>13064</t>
+          <t>13568</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>30351</t>
+          <t>30937</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -9043,12 +9043,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -9063,12 +9063,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>15397</t>
+          <t>15195</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>35208</t>
+          <t>36226</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -9078,12 +9078,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -9098,12 +9098,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>33185</t>
+          <t>32667</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>58883</t>
+          <t>59972</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -9113,12 +9113,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -9141,12 +9141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>14709</t>
+          <t>14255</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9156,12 +9156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7674</t>
+          <t>6800</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9211,12 +9211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>16782</t>
+          <t>17482</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -9254,12 +9254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10984</t>
+          <t>10291</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9269,12 +9269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10136</t>
+          <t>9911</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>26258</t>
+          <t>25777</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9304,12 +9304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9324,12 +9324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>14389</t>
+          <t>13799</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>32047</t>
+          <t>31180</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -9367,12 +9367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>58186</t>
+          <t>57708</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>82549</t>
+          <t>81144</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9382,12 +9382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9402,12 +9402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>73099</t>
+          <t>72052</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>99775</t>
+          <t>100825</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9417,12 +9417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>138912</t>
+          <t>137372</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>175659</t>
+          <t>175773</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>54,95%</t>
         </is>
       </c>
     </row>
@@ -9480,12 +9480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>28961</t>
+          <t>29894</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>49850</t>
+          <t>51406</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9515,12 +9515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>14743</t>
+          <t>14884</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>34561</t>
+          <t>34205</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9530,12 +9530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9550,12 +9550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>48129</t>
+          <t>49823</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>79242</t>
+          <t>79484</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,85%</t>
         </is>
       </c>
     </row>
@@ -9710,12 +9710,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>58515</t>
+          <t>59155</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>97974</t>
+          <t>96707</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9725,12 +9725,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>51901</t>
+          <t>52854</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>83976</t>
+          <t>84968</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9760,12 +9760,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>119438</t>
+          <t>123299</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>169762</t>
+          <t>172620</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -9823,12 +9823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>299810</t>
+          <t>299968</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>366852</t>
+          <t>366867</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -9858,12 +9858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>127982</t>
+          <t>127067</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>173888</t>
+          <t>173185</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9873,12 +9873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9893,12 +9893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>441480</t>
+          <t>437395</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>525221</t>
+          <t>526131</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -9936,12 +9936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>30837</t>
+          <t>31257</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>59566</t>
+          <t>60175</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9951,49 +9951,49 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>11476</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>5991</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>20841</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
           <t>2,22%</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>11476</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>5456</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>20109</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
           <t>50</t>
@@ -10006,12 +10006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>41585</t>
+          <t>40744</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>73356</t>
+          <t>73582</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10021,12 +10021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -10049,12 +10049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>18827</t>
+          <t>18590</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>40694</t>
+          <t>41976</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10064,12 +10064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10084,12 +10084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>53432</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>88453</t>
+          <t>87301</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10104,7 +10104,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10119,12 +10119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>76384</t>
+          <t>76748</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>117703</t>
+          <t>118006</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10134,12 +10134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -10162,12 +10162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>342095</t>
+          <t>340594</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>405357</t>
+          <t>408218</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10197,12 +10197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>315662</t>
+          <t>315312</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>377319</t>
+          <t>375967</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10212,12 +10212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10232,12 +10232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>678490</t>
+          <t>677740</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>768631</t>
+          <t>767122</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10247,12 +10247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,93%</t>
         </is>
       </c>
     </row>
@@ -10275,12 +10275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>494579</t>
+          <t>497830</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>571213</t>
+          <t>571310</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -10310,12 +10310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>270507</t>
+          <t>268588</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>329850</t>
+          <t>327009</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10325,12 +10325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10345,12 +10345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>780944</t>
+          <t>777984</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>877448</t>
+          <t>874497</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,53%</t>
         </is>
       </c>
     </row>
@@ -10738,12 +10738,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29348</t>
+          <t>29901</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53881</t>
+          <t>54098</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10753,12 +10753,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10773,12 +10773,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10155</t>
+          <t>11107</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28407</t>
+          <t>27901</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10788,12 +10788,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10808,12 +10808,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44775</t>
+          <t>44966</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75713</t>
+          <t>75446</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10823,12 +10823,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -10851,12 +10851,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12297</t>
+          <t>13009</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30838</t>
+          <t>31813</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10886,12 +10886,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24824</t>
+          <t>24549</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47327</t>
+          <t>46446</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10901,12 +10901,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10921,12 +10921,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42694</t>
+          <t>41863</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>71747</t>
+          <t>72658</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10936,12 +10936,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -10964,12 +10964,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12428</t>
+          <t>11309</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>6734</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11019,7 +11019,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11034,12 +11034,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2578</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14614</t>
+          <t>14571</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11049,12 +11049,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -11077,12 +11077,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13787</t>
+          <t>15001</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11092,47 +11092,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>5,54%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>16562</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10587</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>25454</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>5,09%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>16562</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>9576</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>25523</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,96%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11147,12 +11147,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16035</t>
+          <t>15983</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34878</t>
+          <t>34700</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11162,12 +11162,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -11190,12 +11190,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99286</t>
+          <t>97871</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>134381</t>
+          <t>131468</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>79658</t>
+          <t>80470</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>108834</t>
+          <t>109661</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11260,12 +11260,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>187876</t>
+          <t>189428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>231192</t>
+          <t>235120</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11275,12 +11275,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>49,11%</t>
         </is>
       </c>
     </row>
@@ -11303,12 +11303,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66641</t>
+          <t>67493</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>98296</t>
+          <t>98075</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11318,12 +11318,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11338,12 +11338,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31678</t>
+          <t>31672</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55193</t>
+          <t>54347</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11373,12 +11373,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>106985</t>
+          <t>106072</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>145656</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11388,12 +11388,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>29,87%</t>
         </is>
       </c>
     </row>
@@ -11533,12 +11533,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13593</t>
+          <t>13791</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32957</t>
+          <t>33604</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17577</t>
+          <t>18336</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11603,12 +11603,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20954</t>
+          <t>19576</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44933</t>
+          <t>43918</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11618,12 +11618,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -11646,12 +11646,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44630</t>
+          <t>44594</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>71336</t>
+          <t>71640</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11661,12 +11661,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11681,12 +11681,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17556</t>
+          <t>16624</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>35592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11696,12 +11696,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11716,12 +11716,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>67145</t>
+          <t>68447</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>99861</t>
+          <t>100521</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11731,12 +11731,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -11764,7 +11764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6513</t>
+          <t>5806</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11779,7 +11779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6794</t>
+          <t>7577</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -11872,12 +11872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10618</t>
+          <t>11159</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11887,12 +11887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11907,12 +11907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5686</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18846</t>
+          <t>19374</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11922,12 +11922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11942,12 +11942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8915</t>
+          <t>9165</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24596</t>
+          <t>25177</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11957,12 +11957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -11985,12 +11985,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47205</t>
+          <t>47251</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>74836</t>
+          <t>74905</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12020,12 +12020,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>66936</t>
+          <t>67104</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>93680</t>
+          <t>95402</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12035,12 +12035,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12055,12 +12055,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>124637</t>
+          <t>123033</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>164097</t>
+          <t>162323</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12070,12 +12070,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,32%</t>
         </is>
       </c>
     </row>
@@ -12098,12 +12098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73315</t>
+          <t>71689</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>104106</t>
+          <t>103914</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12113,12 +12113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12133,12 +12133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40030</t>
+          <t>39264</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62699</t>
+          <t>64261</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12148,12 +12148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12168,12 +12168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>119923</t>
+          <t>121615</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159548</t>
+          <t>160073</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12183,12 +12183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,78%</t>
         </is>
       </c>
     </row>
@@ -12328,12 +12328,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15407</t>
+          <t>15025</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34576</t>
+          <t>35759</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12343,12 +12343,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12363,12 +12363,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15312</t>
+          <t>15858</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12378,12 +12378,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12398,12 +12398,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>22959</t>
+          <t>22631</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>45225</t>
+          <t>45353</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12413,12 +12413,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -12441,12 +12441,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15855</t>
+          <t>15837</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36122</t>
+          <t>36002</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12476,12 +12476,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>964</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10725</t>
+          <t>10496</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12491,12 +12491,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19499</t>
+          <t>19108</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40470</t>
+          <t>40706</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12526,12 +12526,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -12554,12 +12554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>858</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12569,12 +12569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12624,12 +12624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>862</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -12672,7 +12672,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6447</t>
+          <t>8167</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12687,34 +12687,34 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
+          <t>3,96%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>6085</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
           <t>3,13%</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>6283</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -12722,7 +12722,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12742,7 +12742,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t>9662</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12757,7 +12757,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27670</t>
+          <t>28721</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51046</t>
+          <t>51641</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12815,12 +12815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13430</t>
+          <t>12910</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>34332</t>
+          <t>34306</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58407</t>
+          <t>59367</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12865,12 +12865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -12893,12 +12893,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>98201</t>
+          <t>98401</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>127899</t>
+          <t>128317</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12928,12 +12928,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34578</t>
+          <t>33836</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49445</t>
+          <t>49706</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>140920</t>
+          <t>139087</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>173662</t>
+          <t>173373</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12978,12 +12978,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>64,09%</t>
         </is>
       </c>
     </row>
@@ -13123,12 +13123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34625</t>
+          <t>34557</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>60764</t>
+          <t>62188</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13158,12 +13158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29997</t>
+          <t>29711</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>55109</t>
+          <t>55292</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13173,42 +13173,42 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>8,53%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>15,87%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>86683</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>69601</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>105653</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>10,73%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>8,61%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>15,81%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>86683</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>70541</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>105589</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>10,73%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>8,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -13236,12 +13236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>101118</t>
+          <t>102170</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>141511</t>
+          <t>140123</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13271,12 +13271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>63507</t>
+          <t>64475</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>95878</t>
+          <t>94857</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>175765</t>
+          <t>174705</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>227031</t>
+          <t>225354</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13321,12 +13321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -13349,12 +13349,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>7722</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>22708</t>
+          <t>22782</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13364,12 +13364,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -13384,12 +13384,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>993</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>8634</t>
+          <t>9353</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13399,12 +13399,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>10424</t>
+          <t>10264</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>27084</t>
+          <t>27152</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13434,12 +13434,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -13462,12 +13462,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7906</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24296</t>
+          <t>23766</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13477,12 +13477,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13497,12 +13497,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>20464</t>
+          <t>19808</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41582</t>
+          <t>41864</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13512,12 +13512,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>32463</t>
+          <t>32050</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>58665</t>
+          <t>58266</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13547,12 +13547,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -13575,12 +13575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>70877</t>
+          <t>69086</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>102157</t>
+          <t>103045</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13590,12 +13590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>55456</t>
+          <t>56654</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>84304</t>
+          <t>86518</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13625,12 +13625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13645,12 +13645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>134388</t>
+          <t>133627</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>178224</t>
+          <t>177891</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13660,12 +13660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -13688,12 +13688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>160504</t>
+          <t>161760</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>202978</t>
+          <t>202052</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13703,12 +13703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>108446</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>143139</t>
+          <t>143185</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13738,12 +13738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13758,12 +13758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>280704</t>
+          <t>281122</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>333737</t>
+          <t>335099</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13773,12 +13773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,47%</t>
         </is>
       </c>
     </row>
@@ -13918,12 +13918,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8932</t>
+          <t>8577</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26574</t>
+          <t>26143</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13933,12 +13933,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13953,12 +13953,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>31553</t>
+          <t>31698</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>53498</t>
+          <t>53907</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13968,12 +13968,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>45424</t>
+          <t>44896</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>74117</t>
+          <t>73994</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14003,12 +14003,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,98%</t>
         </is>
       </c>
     </row>
@@ -14031,12 +14031,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>21816</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>42144</t>
+          <t>42870</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14046,12 +14046,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -14066,12 +14066,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>10774</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>25633</t>
+          <t>25928</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -14081,12 +14081,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -14101,12 +14101,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>35944</t>
+          <t>35776</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>62189</t>
+          <t>61610</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -14116,12 +14116,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,63%</t>
         </is>
       </c>
     </row>
@@ -14144,12 +14144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>907</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>10138</t>
+          <t>10169</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14184,7 +14184,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6132</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14199,7 +14199,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14214,12 +14214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>11423</t>
+          <t>11298</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14229,12 +14229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -14262,7 +14262,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14277,7 +14277,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14292,12 +14292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8798</t>
+          <t>9151</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>24275</t>
+          <t>25779</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14307,12 +14307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14327,12 +14327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>10617</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>28352</t>
+          <t>26678</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14342,12 +14342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -14370,12 +14370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>66733</t>
+          <t>68308</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>94833</t>
+          <t>95812</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14385,12 +14385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14405,12 +14405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>68821</t>
+          <t>68501</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>95545</t>
+          <t>95482</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14420,12 +14420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14440,12 +14440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>141843</t>
+          <t>144457</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>181794</t>
+          <t>182910</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14455,12 +14455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>49,38%</t>
         </is>
       </c>
     </row>
@@ -14483,12 +14483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>37230</t>
+          <t>37030</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>63629</t>
+          <t>61392</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14498,12 +14498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14518,12 +14518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>22614</t>
+          <t>21966</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>42889</t>
+          <t>42949</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14533,12 +14533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>65519</t>
+          <t>64297</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>97600</t>
+          <t>96830</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14568,12 +14568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,14%</t>
         </is>
       </c>
     </row>
@@ -14713,12 +14713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>125564</t>
+          <t>124040</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>172246</t>
+          <t>172671</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -14728,12 +14728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -14748,12 +14748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>101026</t>
+          <t>100451</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>142573</t>
+          <t>141025</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -14763,12 +14763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -14783,12 +14783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>234584</t>
+          <t>237186</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>300709</t>
+          <t>299926</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -14798,12 +14798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -14826,12 +14826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>222196</t>
+          <t>224029</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>283537</t>
+          <t>281789</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14841,12 +14841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14861,12 +14861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>138189</t>
+          <t>137060</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>185621</t>
+          <t>186441</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14876,12 +14876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14896,12 +14896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>378075</t>
+          <t>374242</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>451018</t>
+          <t>448702</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14911,12 +14911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -14939,12 +14939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>16859</t>
+          <t>16127</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>37784</t>
+          <t>36666</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14954,12 +14954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14974,12 +14974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3087</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>14976</t>
+          <t>14783</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -14989,12 +14989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15009,12 +15009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>23758</t>
+          <t>22681</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>47614</t>
+          <t>46148</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15024,12 +15024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -15052,12 +15052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>22021</t>
+          <t>20860</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>43680</t>
+          <t>44305</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15067,12 +15067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15087,12 +15087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>58771</t>
+          <t>58832</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>92419</t>
+          <t>92265</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15102,12 +15102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15122,12 +15122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>85891</t>
+          <t>85133</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>127439</t>
+          <t>128408</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15137,12 +15137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -15165,12 +15165,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>345134</t>
+          <t>346325</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>411814</t>
+          <t>415061</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15180,12 +15180,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15200,12 +15200,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>302639</t>
+          <t>303798</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>363241</t>
+          <t>360905</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15215,12 +15215,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15235,12 +15235,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>667483</t>
+          <t>668097</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>761347</t>
+          <t>755850</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15250,12 +15250,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -15278,12 +15278,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>478631</t>
+          <t>478852</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>553039</t>
+          <t>551818</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15293,12 +15293,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15313,12 +15313,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>264439</t>
+          <t>264505</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>321462</t>
+          <t>322551</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15328,12 +15328,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15348,12 +15348,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>764641</t>
+          <t>761470</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>855210</t>
+          <t>854127</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15363,12 +15363,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,49%</t>
         </is>
       </c>
     </row>
